--- a/docs/downloads/Windsor.xlsx
+++ b/docs/downloads/Windsor.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D929"/>
+  <dimension ref="A1:D754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ly</t>
+          <t>Halford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wilsonly23@gmail.com</t>
+          <t>playgroundsolutions@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Farinaz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Halford</t>
+          <t>Eftekhari</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>playgroundsolutions@gmail.com</t>
+          <t>eftekharifarinaz@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Farinaz</t>
+          <t>Jaclyn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eftekhari</t>
+          <t>Ricci</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eftekharifarinaz@gmail.com</t>
+          <t>jaclynricci4@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jaclyn</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ricci</t>
+          <t>Capaldi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jaclynricci4@gmail.com</t>
+          <t>events@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capaldi</t>
+          <t>Capogna</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>events@pickleplexclub.ca</t>
+          <t>capogna1998@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capogna</t>
+          <t>Bisson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>capogna1998@gmail.com</t>
+          <t>norm@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bisson</t>
+          <t>Seherba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>norm@pickleplexclub.ca</t>
+          <t>ldseherrba2@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Tyson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Seherba</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ldseherrba2@gmail.com</t>
+          <t>tyson.fisher1@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tyson</t>
+          <t>Anita</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Derose</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tyson.fisher1@gmail.com</t>
+          <t>aderose23@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anita</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Derose</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aderose23@gmail.com</t>
+          <t>edwardbrian3@hotmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Orr</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>orr.andrea@yahoo.com</t>
+          <t>julie.smith@gusrevenberg.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Madeline</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Orr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>madbridesign@yahoo.com</t>
+          <t>orr.andrea@yahoo.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Madeline</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mcgivney</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pmcgiv@hotmail.com</t>
+          <t>madbridesign@yahoo.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luu-hoang</t>
+          <t>Mcgivney</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>luud@uwindsor.ca</t>
+          <t>pmcgiv@hotmail.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pheba</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jithin</t>
+          <t>Luu-hoang</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>diyabi123@gmail.com</t>
+          <t>luud@uwindsor.ca</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Pheba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tonial</t>
+          <t>Jithin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tonial_77@hotmail.com</t>
+          <t>diyabi123@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Briscoe</t>
+          <t>Tonial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>scottgbriscoe@gmail.com</t>
+          <t>tonial_77@hotmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brigitte</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Van westering</t>
+          <t>Briscoe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>henriettevanwestering@gmail.com</t>
+          <t>scottgbriscoe@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Luc</t>
+          <t>Brigitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Van westering</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>luckylucas29@aim.com</t>
+          <t>henriettevanwestering@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Courtney</t>
+          <t>Luc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hawkes</t>
+          <t>Su</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>courtneyhawkess@gmail.com</t>
+          <t>luckylucas29@aim.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Courtney</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Hawkes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>windsor@pickleplexclub.ca</t>
+          <t>courtneyhawkess@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Remi</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Richer</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>remiricher@hotmail.com</t>
+          <t>windsor@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brad</t>
+          <t>Remi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bottoset</t>
+          <t>Richer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bbottoset@gmail.com</t>
+          <t>remiricher@hotmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Louise</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salusny</t>
+          <t>Bottoset</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>louisesal@hotmail.com</t>
+          <t>bbottoset@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Louise</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Halford</t>
+          <t>Salusny</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>annahalf@live.com</t>
+          <t>louisesal@hotmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lazzarin</t>
+          <t>Halford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dsafaf@gmail.com</t>
+          <t>annahalf@live.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Siddharth kumar</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Lazzarin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>presidentsid1311@gmail.com</t>
+          <t>dsafaf@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Arlen</t>
+          <t>Siddharth kumar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Seherba</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>arlenseherba7@gmail.com</t>
+          <t>presidentsid1311@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Arlen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Seherba</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jcljm@duck.com</t>
+          <t>arlenseherba7@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mcarthur</t>
+          <t>Lai</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>capmac91@gmail.com</t>
+          <t>allenlai09@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tymec</t>
+          <t>Mcarthur</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>spiritzz612@gmail.com</t>
+          <t>capmac91@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nayoung</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Tymec</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>skdund1909@naber.com</t>
+          <t>spiritzz612@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vilas ravindra</t>
+          <t>Nayoung</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dulipeta</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>vilasdravindra@gmail.com</t>
+          <t>skdund1909@naber.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Vilas ravindra</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sadik</t>
+          <t>Dulipeta</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>marinasadik28@gmail.com</t>
+          <t>vilasdravindra@gmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Odonkor</t>
+          <t>Sadik</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>graceotiosei@gmail.com</t>
+          <t>marinasadik28@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Odonkor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mikesparty1616@gmail.com</t>
+          <t>graceotiosei@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jackie</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Beaudoin</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ptjakcie@hotmail.com</t>
+          <t>mikesparty1616@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Liz</t>
+          <t>Jackie</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Goncalves</t>
+          <t>Beaudoin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lizarmani@gmail.com</t>
+          <t>ptjakcie@hotmail.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ab</t>
+          <t>Liz</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cde</t>
+          <t>Goncalves</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abc@gmail.com</t>
+          <t>lizarmani@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Ab</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Guzman</t>
+          <t>Cde</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>joseguzman100408@gmail.com</t>
+          <t>abc@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vergel de dios</t>
+          <t>Guzman</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>brian.vergeldedios@gmail.com</t>
+          <t>joseguzman100408@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Vergel de dios</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hfwilson@cogeco.ca</t>
+          <t>brian.vergeldedios@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cecile</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hopetoday10@gmail.com</t>
+          <t>hfwilson@cogeco.ca</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Beaudoin</t>
+          <t>Cecile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>randybeaudoin@hotmail.com</t>
+          <t>hopetoday10@gmail.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Synnott</t>
+          <t>Beaudoin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>norm@mysynnott.net</t>
+          <t>randybeaudoin@hotmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Falconi</t>
+          <t>Synnott</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>lauriefalconi@gmail.com</t>
+          <t>norm@mysynnott.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Meryl</t>
+          <t>Weaam</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dayao</t>
+          <t>Oraha</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>meryldayao@gmail.com</t>
+          <t>weaamoraha@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Weaam</t>
+          <t>Stéphane</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Oraha</t>
+          <t>Lefort</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>weaamoraha@gmail.com</t>
+          <t>stefanlefort@hotmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Stéphane</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lefort</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>stefanlefort@hotmail.com</t>
+          <t>edward@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,19 +1997,15 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>edward@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Branton</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -2019,12 +2015,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Branton</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2037,12 +2033,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Lourd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Handola</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -2055,12 +2051,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lourd</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Handola</t>
+          <t>Kondracki</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2073,12 +2069,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kondracki</t>
+          <t>Marie Bisson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -2091,12 +2087,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Marie Bisson</t>
+          <t>Mayhew</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2109,12 +2105,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mayhew</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2127,12 +2123,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Domenic</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Chimienti</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2145,12 +2141,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Domenic</t>
+          <t>Paisley</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chimienti</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2163,12 +2159,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Paisley</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Cervi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2181,12 +2177,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cervi</t>
+          <t>Su</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2199,12 +2195,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2217,12 +2213,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Belcastro</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2235,12 +2231,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Belcastro</t>
+          <t>Boulanger</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2253,12 +2249,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Boulanger</t>
+          <t>Dinunzio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2271,12 +2267,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Tilly</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dinunzio</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2289,12 +2285,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tilly</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Burk</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2307,12 +2303,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Burk</t>
+          <t>Abi-Samra</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2325,12 +2321,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Shelley</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Abi-Samra</t>
+          <t>Cazzola</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2343,12 +2339,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Shelley</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cazzola</t>
+          <t>Beaudoin</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2361,12 +2357,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Beaudoin</t>
+          <t>Marie Bisson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2379,12 +2375,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Marie Bisson</t>
+          <t>Lan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2397,12 +2393,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Kiera</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lan</t>
+          <t>Su</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2415,12 +2411,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kiera</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Bieniewski</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2433,12 +2429,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Brayden</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bieniewski</t>
+          <t>Kanally</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2451,12 +2447,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Brayden</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kanally</t>
+          <t>Talbot-Benvenuto</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2469,12 +2465,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Bashar</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Talbot-Benvenuto</t>
+          <t>Handola</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2487,12 +2483,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bashar</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Handola</t>
+          <t>Lan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2505,12 +2501,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Domenyk</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lan</t>
+          <t>Dinunzio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2523,12 +2519,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Domenyk</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dinunzio</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2541,7 +2537,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2559,12 +2555,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Huynh</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2577,12 +2573,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Yee</t>
+          <t>Ouellette</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2595,12 +2591,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ouellette</t>
+          <t>Burk</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2613,12 +2609,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Burk</t>
+          <t>Dinh</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2631,12 +2627,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dinh</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2649,12 +2645,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Huynh</t>
+          <t>Haesler</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2667,12 +2663,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Alfredo</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Haesler</t>
+          <t>Dinunzio</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2685,12 +2681,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Alfredo</t>
+          <t>Aviva</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dinunzio</t>
+          <t>Guttman</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2703,12 +2699,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Aviva</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Guttman</t>
+          <t>Thivierge</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2721,12 +2717,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Ryan JR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Thivierge</t>
+          <t>Guthrie</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2739,12 +2735,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ryan JR</t>
+          <t>Norm Jr`</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Guthrie</t>
+          <t>yetman</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2757,12 +2753,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Norm Jr`</t>
+          <t>Ryan Jr</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>yetman</t>
+          <t>Scarfone</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2775,12 +2771,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ryan Jr</t>
+          <t>Xuyen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Scarfone</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2793,12 +2789,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Xuyen</t>
+          <t>Hussayn</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Reslan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2811,12 +2807,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Hussayn</t>
+          <t>Ersilia</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Reslan</t>
+          <t>Dinunzio</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2829,12 +2825,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ersilia</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dinunzio</t>
+          <t>LaBonte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2847,12 +2843,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Gregoris</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LaBonte</t>
+          <t>Senteris</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2865,12 +2861,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Gregoris</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Senteris</t>
+          <t>cascio</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2883,12 +2879,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Rudra</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cascio</t>
+          <t>Shankar</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2901,12 +2897,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Rudra</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Shankar</t>
+          <t>Guerrieri</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2919,12 +2915,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Sayde</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Guerrieri</t>
+          <t>Abi-Samra</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2937,12 +2933,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sayde</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Abi-Samra</t>
+          <t>Beaudoin</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2955,12 +2951,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Beaudoin</t>
+          <t>Figueroa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2973,12 +2969,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Lina</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Figueroa</t>
+          <t>Bucciarelli</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2991,12 +2987,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Lina</t>
+          <t>Eliseo</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bucciarelli</t>
+          <t>Talbot-Benvenuto</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3009,12 +3005,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Eliseo</t>
+          <t>Emet</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Talbot-Benvenuto</t>
+          <t>Guttman</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3027,12 +3023,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Emet</t>
+          <t>Leah</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Guttman</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3045,12 +3041,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Leah</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Yee</t>
+          <t>Talbot</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3063,12 +3059,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Talbot</t>
+          <t>Dewedar</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3081,12 +3077,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Lexi</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dewedar</t>
+          <t>Thivierge</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3099,12 +3095,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Lexi</t>
+          <t>Thao</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Thivierge</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3117,12 +3113,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Thao</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Gresser</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3135,12 +3131,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Gresser</t>
+          <t>Baltador</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3153,12 +3149,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Baltador</t>
+          <t>Marie Bisson</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3171,12 +3167,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Marie Bisson</t>
+          <t>Sepetanc</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3189,12 +3185,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Mika</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sepetanc</t>
+          <t>Lai</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3207,12 +3203,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mika</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lai</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3225,12 +3221,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Doe</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3243,12 +3239,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Doe</t>
+          <t>Rau</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3261,12 +3257,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rau</t>
+          <t>Gobbato</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3279,12 +3275,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Gobbato</t>
+          <t>Marie Bisson</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3297,12 +3293,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Marie Bisson</t>
+          <t>Stevenson</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3315,12 +3311,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stevenson</t>
+          <t>McLennan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3333,12 +3329,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>McLennan</t>
+          <t>Burns</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3351,12 +3347,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Bianca</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Burns</t>
+          <t>Baltador</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3369,7 +3365,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Bianca</t>
+          <t>Alina</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3387,12 +3383,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alina</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Baltador</t>
+          <t>Branton</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3405,12 +3401,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Branton</t>
+          <t>Krauter</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3423,12 +3419,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Marie-Louise</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Krauter</t>
+          <t>Burey</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3441,12 +3437,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Marie-Louise</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Burey</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3459,12 +3455,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Huynh</t>
+          <t>Garrod</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3477,12 +3473,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Garrod</t>
+          <t>kim</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3495,12 +3491,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>kim</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3513,12 +3509,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Lua</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Sepetance</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3531,12 +3527,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Lua</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sepetance</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3549,12 +3545,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Maude</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Huynh</t>
+          <t>Poulin</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3567,12 +3563,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Maude</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Poulin</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3585,12 +3581,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Wyatt</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Bechard</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3603,12 +3599,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Wyatt</t>
+          <t>Brody</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Bechard</t>
+          <t>Tynkaluk</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3621,12 +3617,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Brody</t>
+          <t>Alexis</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tynkaluk</t>
+          <t>Parent</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3639,12 +3635,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Alexis</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3657,12 +3653,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Huynh</t>
+          <t>Manimtim</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3675,12 +3671,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Cayden</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Manimtim</t>
+          <t>Khandoker</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3693,7 +3689,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cayden</t>
+          <t>Naudia</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3711,12 +3707,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Naudia</t>
+          <t>Davin</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Khandoker</t>
+          <t>Keyeux</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3729,15 +3725,19 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Davin</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Keyeux</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>Saffran</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>cathsaffran@gmail.com</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -3747,19 +3747,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Milad</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Saffran</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>cathsaffran@gmail.com</t>
-        </is>
-      </c>
+          <t>Khouri</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -3769,15 +3765,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Milad</t>
+          <t>Bret</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Khouri</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Riesberry</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>bretriesberry@gmail.com</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13325,19 +13325,15 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="C700" t="inlineStr">
-        <is>
-          <t>ktaylor@bdo.ca</t>
-        </is>
-      </c>
+          <t>Samwel</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13347,12 +13343,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Gigi</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Samwel</t>
+          <t>Geary</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -13365,12 +13361,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Gigi</t>
+          <t>Sloane</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Geary</t>
+          <t>O’Hagan</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -13383,12 +13379,12 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Sloane</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>O’Hagan</t>
+          <t>Rauth</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -13401,12 +13397,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Rauth</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -13419,12 +13415,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Dion</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -13437,12 +13433,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Dion</t>
+          <t>Renaud</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -13455,12 +13451,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Kensington</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Renaud</t>
+          <t>Vrbjar</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -13473,12 +13469,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Kensington</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Vrbjar</t>
+          <t>Zold</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -13491,12 +13487,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Scotlyn</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Zold</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -13509,12 +13505,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Scotlyn</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Yassine</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -13527,15 +13523,19 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Sabine</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Yassine</t>
-        </is>
-      </c>
-      <c r="C711" t="inlineStr"/>
+          <t>Rayes</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>rayessabine@gmail.com</t>
+        </is>
+      </c>
       <c r="D711" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13545,19 +13545,15 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Sabine</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Rayes</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>rayessabine@gmail.com</t>
-        </is>
-      </c>
+          <t>piper</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13567,7 +13563,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Juniper</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -13585,7 +13581,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Juniper</t>
+          <t>Callie</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -13603,15 +13599,19 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Callie</t>
+          <t>Tonia</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>piper</t>
-        </is>
-      </c>
-      <c r="C715" t="inlineStr"/>
+          <t>Bryans</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>bermudagirl5@icould.com</t>
+        </is>
+      </c>
       <c r="D715" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13621,19 +13621,15 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Madelins</t>
+          <t>Beesan</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Cherian</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>maddycherian@gmail.com</t>
-        </is>
-      </c>
+          <t>Jarrar</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13643,19 +13639,15 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Clinton</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Smit</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr">
-        <is>
-          <t>clintonsmit24@gmail.com</t>
-        </is>
-      </c>
+          <t>Manlongat</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13665,19 +13657,15 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Mitch</t>
+          <t>Fynn</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Goodwin</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>goodwin_4u@yahoo.ca</t>
-        </is>
-      </c>
+          <t>Manlongat</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13687,19 +13675,15 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Hooft</t>
-        </is>
-      </c>
-      <c r="C719" t="inlineStr">
-        <is>
-          <t>a.n.hooft@gmail.com</t>
-        </is>
-      </c>
+          <t>Manlongat</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13709,19 +13693,15 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Lina</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Alshimmari</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t>lalshimm@gmail.com</t>
-        </is>
-      </c>
+          <t>Foglia</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13731,19 +13711,15 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Parris</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>parrisdallia@gmail.com</t>
-        </is>
-      </c>
+          <t>Addai</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13753,19 +13729,15 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Omer</t>
+          <t>Adrien</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Bico</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>biom548@gmail.com</t>
-        </is>
-      </c>
+          <t>Addai</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13775,19 +13747,15 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Shanmugam</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Viswanathan</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>akron1996@gmail.com</t>
-        </is>
-      </c>
+          <t>St. pierre</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13797,19 +13765,15 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Abdul Rafey</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Mehmood</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>abdulrafeyca@hotmail.com</t>
-        </is>
-      </c>
+          <t>st. pierre</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13819,19 +13783,15 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>elisabeth</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>remington</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>ejournalist21@gmail.com</t>
-        </is>
-      </c>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13841,19 +13801,15 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Ng</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t>footbalhk+pickleplex@gmail.com</t>
-        </is>
-      </c>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13863,19 +13819,15 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Storino</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>marcstorino@yahoo.com</t>
-        </is>
-      </c>
+          <t>Monroy</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13885,19 +13837,15 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Jax</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Palamides</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>epal1642@gmail.com</t>
-        </is>
-      </c>
+          <t>Wasilewski</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13907,19 +13855,15 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Yuvraj Singh</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Bhatti</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>yuvrajsinghbhatti@gmail.com</t>
-        </is>
-      </c>
+          <t>Monroy</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13929,19 +13873,15 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Fernanda</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>McKnight</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr">
-        <is>
-          <t>kimstroesser@gmail.com</t>
-        </is>
-      </c>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13951,19 +13891,15 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Karthik</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Kasi</t>
-        </is>
-      </c>
-      <c r="C731" t="inlineStr">
-        <is>
-          <t>kasikgns@gmail.com</t>
-        </is>
-      </c>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13973,19 +13909,15 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Tangi</t>
+          <t>Aleah</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Arora</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>tanvi14arora@gmail.com</t>
-        </is>
-      </c>
+          <t>Wasilewski</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -13995,19 +13927,15 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Rahul</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Chitre</t>
-        </is>
-      </c>
-      <c r="C733" t="inlineStr">
-        <is>
-          <t>rahulrajan.chitre@valianttms.com</t>
-        </is>
-      </c>
+          <t>Sauro</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14017,17 +13945,17 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Luigi</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Vani</t>
+          <t>Lue Pann</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>vanil1535@gmail.com</t>
+          <t>nmluepann@gmail.com</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -14039,19 +13967,15 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>Tonia</t>
+          <t>Macaelle Ricci</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Bryans</t>
-        </is>
-      </c>
-      <c r="C735" t="inlineStr">
-        <is>
-          <t>bermudagirl5@icould.com</t>
-        </is>
-      </c>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14061,19 +13985,15 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Mohammad</t>
+          <t>Chael Sebastian</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Hadwan</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
-        <is>
-          <t>moehdwan@gmail.com</t>
-        </is>
-      </c>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14083,19 +14003,15 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Charmaine</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Teasdale</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t>connorwateasdale@gmail.com</t>
-        </is>
-      </c>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14105,15 +14021,19 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Beesan</t>
+          <t>adam</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Jarrar</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr"/>
+          <t>bisson</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>adambison@pickleplex.ca</t>
+        </is>
+      </c>
       <c r="D738" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14123,17 +14043,17 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Dawsyn</t>
+          <t>Meet</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Lefebvre</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>kippfudge@gmail.com</t>
+          <t>meetpatel@nextstar-energy.com</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -14145,17 +14065,17 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Geoffrey</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Hadwan</t>
+          <t>MacNeil</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>alihadwan22@gmail.com</t>
+          <t>geoffreymacneil3@gmaikl.com</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -14167,19 +14087,15 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>Hadi</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Elsiblani</t>
-        </is>
-      </c>
-      <c r="C741" t="inlineStr">
-        <is>
-          <t>hadie2428@gmail.com</t>
-        </is>
-      </c>
+          <t>Gillis</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14189,19 +14105,15 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Gutierrez</t>
-        </is>
-      </c>
-      <c r="C742" t="inlineStr">
-        <is>
-          <t>d1_leon@hotmail.com</t>
-        </is>
-      </c>
+          <t>Comartin</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14211,19 +14123,15 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>Behzad</t>
+          <t>Jaxtyn</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Eskandari</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr">
-        <is>
-          <t>b.eskandari65@gmail.com</t>
-        </is>
-      </c>
+          <t>Kamath</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14233,17 +14141,17 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Demetri</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>El-siblani</t>
+          <t>Vacratsis</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>ibr.sbl05@gmail.com</t>
+          <t>vacratsis@gmail.com</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -14255,19 +14163,15 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Al-Hassanawi</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr">
-        <is>
-          <t>m35744417@gmail.com</t>
-        </is>
-      </c>
+          <t>Ledoux</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14277,19 +14181,15 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>Mohamad</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Korraali</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>mkorraali@gmail.com</t>
-        </is>
-      </c>
+          <t>Leblanc</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14299,19 +14199,15 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>Nicklaus</t>
+          <t>sophia</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Bondy</t>
-        </is>
-      </c>
-      <c r="C747" t="inlineStr">
-        <is>
-          <t>nickbondy@outlook.com</t>
-        </is>
-      </c>
+          <t>Decker</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14321,19 +14217,15 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>julia</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Kocavs</t>
-        </is>
-      </c>
-      <c r="C748" t="inlineStr">
-        <is>
-          <t>dkovacs2005@yahoo.ca</t>
-        </is>
-      </c>
+          <t>Proc</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14343,19 +14235,15 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Nazare</t>
+          <t>jackie</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Muniz Rodriguez</t>
-        </is>
-      </c>
-      <c r="C749" t="inlineStr">
-        <is>
-          <t>nazaremuniz@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Proc</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14365,19 +14253,15 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Tonia</t>
+          <t>vivian</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Bryans</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>bermudagirl5@icloud.com</t>
-        </is>
-      </c>
+          <t>Leblanc</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14387,19 +14271,15 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>Emile</t>
+          <t>Sherri</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Jabbour</t>
-        </is>
-      </c>
-      <c r="C751" t="inlineStr">
-        <is>
-          <t>emile.jabbour93@gmail.com</t>
-        </is>
-      </c>
+          <t>Ledoux</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14409,19 +14289,15 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>Hiba</t>
+          <t>Nayiya</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Al-bousaleh</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr">
-        <is>
-          <t>bubbles01h@gmail.com</t>
-        </is>
-      </c>
+          <t>Bourdeau</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14431,19 +14307,15 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>Deeksha</t>
+          <t>Allie</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Vashisht</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
-        <is>
-          <t>deeksha.vashisht@valianttms.com</t>
-        </is>
-      </c>
+          <t>Bourdeau</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
@@ -14453,3790 +14325,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Andrew Stewart</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>McCarthy</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr">
-        <is>
-          <t>dpmccarthy14@gmail.com</t>
-        </is>
-      </c>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>Xavier</t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>Manlongat</t>
-        </is>
-      </c>
-      <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>Montgomery</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr">
-        <is>
-          <t>jomontgo16@gmail.com</t>
-        </is>
-      </c>
-      <c r="D756" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>Audrie</t>
-        </is>
-      </c>
-      <c r="B757" t="inlineStr">
-        <is>
-          <t>Cormier</t>
-        </is>
-      </c>
-      <c r="C757" t="inlineStr">
-        <is>
-          <t>audriecormier6@gmail.com</t>
-        </is>
-      </c>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>Renee</t>
-        </is>
-      </c>
-      <c r="B758" t="inlineStr">
-        <is>
-          <t>McLeod</t>
-        </is>
-      </c>
-      <c r="C758" t="inlineStr">
-        <is>
-          <t>rmcleod021@gmail.com</t>
-        </is>
-      </c>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>brooke</t>
-        </is>
-      </c>
-      <c r="B759" t="inlineStr">
-        <is>
-          <t>shepley</t>
-        </is>
-      </c>
-      <c r="C759" t="inlineStr">
-        <is>
-          <t>brookelauren2007@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>Maggie</t>
-        </is>
-      </c>
-      <c r="B760" t="inlineStr">
-        <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C760" t="inlineStr">
-        <is>
-          <t>xmaggiechan@gmail.com</t>
-        </is>
-      </c>
-      <c r="D760" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B761" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="C761" t="inlineStr">
-        <is>
-          <t>aarondrew_23@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>Fynn</t>
-        </is>
-      </c>
-      <c r="B762" t="inlineStr">
-        <is>
-          <t>Manlongat</t>
-        </is>
-      </c>
-      <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>Roman</t>
-        </is>
-      </c>
-      <c r="B763" t="inlineStr">
-        <is>
-          <t>Manlongat</t>
-        </is>
-      </c>
-      <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="B764" t="inlineStr">
-        <is>
-          <t>Mailloux</t>
-        </is>
-      </c>
-      <c r="C764" t="inlineStr">
-        <is>
-          <t>nicole.alexandra@hotmail.ca</t>
-        </is>
-      </c>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>Kristina</t>
-        </is>
-      </c>
-      <c r="B765" t="inlineStr">
-        <is>
-          <t>Ivanova</t>
-        </is>
-      </c>
-      <c r="C765" t="inlineStr">
-        <is>
-          <t>ivanova_kristina10@icloud.com</t>
-        </is>
-      </c>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>Abbey</t>
-        </is>
-      </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t>Gradwell</t>
-        </is>
-      </c>
-      <c r="C766" t="inlineStr">
-        <is>
-          <t>abbeygradwell_98@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>Abdulhadi</t>
-        </is>
-      </c>
-      <c r="B767" t="inlineStr">
-        <is>
-          <t>Habib</t>
-        </is>
-      </c>
-      <c r="C767" t="inlineStr">
-        <is>
-          <t>abdulhad.habib777@gmail.com</t>
-        </is>
-      </c>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
-        <is>
-          <t>Maaz</t>
-        </is>
-      </c>
-      <c r="B768" t="inlineStr">
-        <is>
-          <t>Hussain</t>
-        </is>
-      </c>
-      <c r="C768" t="inlineStr">
-        <is>
-          <t>maazhussain52@gmail.com</t>
-        </is>
-      </c>
-      <c r="D768" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
-        <is>
-          <t>Kelsey</t>
-        </is>
-      </c>
-      <c r="B769" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="C769" t="inlineStr">
-        <is>
-          <t>white125@uwindsor.ca</t>
-        </is>
-      </c>
-      <c r="D769" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
-        <is>
-          <t>Aleksandar</t>
-        </is>
-      </c>
-      <c r="B770" t="inlineStr">
-        <is>
-          <t>Miloyevich</t>
-        </is>
-      </c>
-      <c r="C770" t="inlineStr">
-        <is>
-          <t>miloyevichaleks@gmail.com</t>
-        </is>
-      </c>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
-        <is>
-          <t>Hassaan</t>
-        </is>
-      </c>
-      <c r="B771" t="inlineStr">
-        <is>
-          <t>Ahmed</t>
-        </is>
-      </c>
-      <c r="C771" t="inlineStr">
-        <is>
-          <t>hassaan.sauga96@gmail.com</t>
-        </is>
-      </c>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
-        <is>
-          <t>Hussein</t>
-        </is>
-      </c>
-      <c r="B772" t="inlineStr">
-        <is>
-          <t>Kothari</t>
-        </is>
-      </c>
-      <c r="C772" t="inlineStr">
-        <is>
-          <t>kotari.hussein@gmail.com</t>
-        </is>
-      </c>
-      <c r="D772" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B773" t="inlineStr">
-        <is>
-          <t>St Louis</t>
-        </is>
-      </c>
-      <c r="C773" t="inlineStr">
-        <is>
-          <t>stephenstlouis@gmail.com</t>
-        </is>
-      </c>
-      <c r="D773" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
-        <is>
-          <t>Zana</t>
-        </is>
-      </c>
-      <c r="B774" t="inlineStr">
-        <is>
-          <t>Taka</t>
-        </is>
-      </c>
-      <c r="C774" t="inlineStr">
-        <is>
-          <t>zanataka29@gmail.com</t>
-        </is>
-      </c>
-      <c r="D774" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
-        <is>
-          <t>Ronald</t>
-        </is>
-      </c>
-      <c r="B775" t="inlineStr">
-        <is>
-          <t>Addai</t>
-        </is>
-      </c>
-      <c r="C775" t="inlineStr">
-        <is>
-          <t>ronaldaddai@gmail.com</t>
-        </is>
-      </c>
-      <c r="D775" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="B776" t="inlineStr">
-        <is>
-          <t>Foglia</t>
-        </is>
-      </c>
-      <c r="C776" t="inlineStr"/>
-      <c r="D776" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
-        <is>
-          <t>Chris</t>
-        </is>
-      </c>
-      <c r="B777" t="inlineStr">
-        <is>
-          <t>Gelinas</t>
-        </is>
-      </c>
-      <c r="C777" t="inlineStr">
-        <is>
-          <t>chris@autoeverything.ca</t>
-        </is>
-      </c>
-      <c r="D777" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="B778" t="inlineStr">
-        <is>
-          <t>Foglia</t>
-        </is>
-      </c>
-      <c r="C778" t="inlineStr">
-        <is>
-          <t>jnfoglia@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D778" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="B779" t="inlineStr">
-        <is>
-          <t>Addai</t>
-        </is>
-      </c>
-      <c r="C779" t="inlineStr">
-        <is>
-          <t>crystaladdai9@gmail.com</t>
-        </is>
-      </c>
-      <c r="D779" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>Reem</t>
-        </is>
-      </c>
-      <c r="B780" t="inlineStr">
-        <is>
-          <t>Taka</t>
-        </is>
-      </c>
-      <c r="C780" t="inlineStr">
-        <is>
-          <t>reem.taka@gmail.com</t>
-        </is>
-      </c>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>Andre</t>
-        </is>
-      </c>
-      <c r="B781" t="inlineStr">
-        <is>
-          <t>Addai</t>
-        </is>
-      </c>
-      <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>taym</t>
-        </is>
-      </c>
-      <c r="B782" t="inlineStr">
-        <is>
-          <t>taka</t>
-        </is>
-      </c>
-      <c r="C782" t="inlineStr">
-        <is>
-          <t>taymtaka2@gmail.com</t>
-        </is>
-      </c>
-      <c r="D782" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
-        <is>
-          <t>Aws</t>
-        </is>
-      </c>
-      <c r="B783" t="inlineStr">
-        <is>
-          <t>Taka</t>
-        </is>
-      </c>
-      <c r="C783" t="inlineStr">
-        <is>
-          <t>aws.taka@gmail.com</t>
-        </is>
-      </c>
-      <c r="D783" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
-        <is>
-          <t>Adrien</t>
-        </is>
-      </c>
-      <c r="B784" t="inlineStr">
-        <is>
-          <t>Addai</t>
-        </is>
-      </c>
-      <c r="C784" t="inlineStr"/>
-      <c r="D784" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
-        <is>
-          <t>Loris</t>
-        </is>
-      </c>
-      <c r="B785" t="inlineStr">
-        <is>
-          <t>Sandre</t>
-        </is>
-      </c>
-      <c r="C785" t="inlineStr">
-        <is>
-          <t>1952lasandre@gmail.com</t>
-        </is>
-      </c>
-      <c r="D785" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>St. pierre</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr"/>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>Mel</t>
-        </is>
-      </c>
-      <c r="B787" t="inlineStr">
-        <is>
-          <t>Silj</t>
-        </is>
-      </c>
-      <c r="C787" t="inlineStr">
-        <is>
-          <t>msiljanovski@intsoftgels.com</t>
-        </is>
-      </c>
-      <c r="D787" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>Joe</t>
-        </is>
-      </c>
-      <c r="B788" t="inlineStr">
-        <is>
-          <t>Foisey</t>
-        </is>
-      </c>
-      <c r="C788" t="inlineStr">
-        <is>
-          <t>jfoisey@cogeco.ca</t>
-        </is>
-      </c>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="B789" t="inlineStr">
-        <is>
-          <t>Lepore</t>
-        </is>
-      </c>
-      <c r="C789" t="inlineStr">
-        <is>
-          <t>mileslepore@icoud.com</t>
-        </is>
-      </c>
-      <c r="D789" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
-        <is>
-          <t>MADELINE</t>
-        </is>
-      </c>
-      <c r="B790" t="inlineStr">
-        <is>
-          <t>LITWILLER</t>
-        </is>
-      </c>
-      <c r="C790" t="inlineStr">
-        <is>
-          <t>maddielitwiller@gmail.com</t>
-        </is>
-      </c>
-      <c r="D790" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
-        <is>
-          <t>Cary</t>
-        </is>
-      </c>
-      <c r="B791" t="inlineStr">
-        <is>
-          <t>Neveu</t>
-        </is>
-      </c>
-      <c r="C791" t="inlineStr">
-        <is>
-          <t>caryneveu101@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D791" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
-        <is>
-          <t>Brooklyn</t>
-        </is>
-      </c>
-      <c r="B792" t="inlineStr">
-        <is>
-          <t>st. pierre</t>
-        </is>
-      </c>
-      <c r="C792" t="inlineStr"/>
-      <c r="D792" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
-        <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="B793" t="inlineStr">
-        <is>
-          <t>Heath</t>
-        </is>
-      </c>
-      <c r="C793" t="inlineStr">
-        <is>
-          <t>mikedheath@proton.me</t>
-        </is>
-      </c>
-      <c r="D793" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>Tambudzai</t>
-        </is>
-      </c>
-      <c r="B794" t="inlineStr">
-        <is>
-          <t>Kasiyamhuru</t>
-        </is>
-      </c>
-      <c r="C794" t="inlineStr">
-        <is>
-          <t>tbkasiyamhuru@gmail.com</t>
-        </is>
-      </c>
-      <c r="D794" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="B795" t="inlineStr">
-        <is>
-          <t>Mancini</t>
-        </is>
-      </c>
-      <c r="C795" t="inlineStr">
-        <is>
-          <t>crystalmancini@gmail.com</t>
-        </is>
-      </c>
-      <c r="D795" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="B796" t="inlineStr">
-        <is>
-          <t>Stiller</t>
-        </is>
-      </c>
-      <c r="C796" t="inlineStr">
-        <is>
-          <t>xsarastillyy@gmail.com</t>
-        </is>
-      </c>
-      <c r="D796" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
-        <is>
-          <t>Brandon</t>
-        </is>
-      </c>
-      <c r="B797" t="inlineStr">
-        <is>
-          <t>Borrelli</t>
-        </is>
-      </c>
-      <c r="C797" t="inlineStr">
-        <is>
-          <t>brandonborrelli@gmail.com</t>
-        </is>
-      </c>
-      <c r="D797" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
-        <is>
-          <t>Philippe</t>
-        </is>
-      </c>
-      <c r="B798" t="inlineStr">
-        <is>
-          <t>Raymomd</t>
-        </is>
-      </c>
-      <c r="C798" t="inlineStr">
-        <is>
-          <t>philippemraymond@gmail.com</t>
-        </is>
-      </c>
-      <c r="D798" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
-      <c r="B799" t="inlineStr">
-        <is>
-          <t>Peach</t>
-        </is>
-      </c>
-      <c r="C799" t="inlineStr">
-        <is>
-          <t>al_peach@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D799" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
-        <is>
-          <t>Radomir</t>
-        </is>
-      </c>
-      <c r="B800" t="inlineStr">
-        <is>
-          <t>Jovanovic</t>
-        </is>
-      </c>
-      <c r="C800" t="inlineStr">
-        <is>
-          <t>alo-uzice@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D800" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
-        <is>
-          <t>George</t>
-        </is>
-      </c>
-      <c r="B801" t="inlineStr">
-        <is>
-          <t>Barhoum</t>
-        </is>
-      </c>
-      <c r="C801" t="inlineStr">
-        <is>
-          <t>georgebarhoum08@gmail.com</t>
-        </is>
-      </c>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
-        <is>
-          <t>Matteo</t>
-        </is>
-      </c>
-      <c r="B802" t="inlineStr">
-        <is>
-          <t>Mady</t>
-        </is>
-      </c>
-      <c r="C802" t="inlineStr">
-        <is>
-          <t>matteomady2012@gmail.com</t>
-        </is>
-      </c>
-      <c r="D802" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
-        <is>
-          <t>Bradly</t>
-        </is>
-      </c>
-      <c r="B803" t="inlineStr">
-        <is>
-          <t>Kizigenza</t>
-        </is>
-      </c>
-      <c r="C803" t="inlineStr">
-        <is>
-          <t>kizigenzabradly@gmail.com</t>
-        </is>
-      </c>
-      <c r="D803" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B804" t="inlineStr">
-        <is>
-          <t>Peach</t>
-        </is>
-      </c>
-      <c r="C804" t="inlineStr">
-        <is>
-          <t>c.peach2009@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D804" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
-        <is>
-          <t>Mirjana</t>
-        </is>
-      </c>
-      <c r="B805" t="inlineStr">
-        <is>
-          <t>Gordic</t>
-        </is>
-      </c>
-      <c r="C805" t="inlineStr">
-        <is>
-          <t>ergub1@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D805" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
-        <is>
-          <t>Goran</t>
-        </is>
-      </c>
-      <c r="B806" t="inlineStr">
-        <is>
-          <t>Trakilovic</t>
-        </is>
-      </c>
-      <c r="C806" t="inlineStr">
-        <is>
-          <t>gtrakilovic@gmial.com</t>
-        </is>
-      </c>
-      <c r="D806" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-      <c r="B807" t="inlineStr">
-        <is>
-          <t>Ray</t>
-        </is>
-      </c>
-      <c r="C807" t="inlineStr">
-        <is>
-          <t>amberray595@gmail.com</t>
-        </is>
-      </c>
-      <c r="D807" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
-        <is>
-          <t>Kyle</t>
-        </is>
-      </c>
-      <c r="B808" t="inlineStr">
-        <is>
-          <t>Marchand</t>
-        </is>
-      </c>
-      <c r="C808" t="inlineStr">
-        <is>
-          <t>kyledmarchand@gmail.com</t>
-        </is>
-      </c>
-      <c r="D808" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>Ava</t>
-        </is>
-      </c>
-      <c r="B809" t="inlineStr">
-        <is>
-          <t>Goudie</t>
-        </is>
-      </c>
-      <c r="C809" t="inlineStr">
-        <is>
-          <t>ava.goudie13@gmail.com</t>
-        </is>
-      </c>
-      <c r="D809" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="B810" t="inlineStr">
-        <is>
-          <t>Dumouchelle</t>
-        </is>
-      </c>
-      <c r="C810" t="inlineStr">
-        <is>
-          <t>briannahdumouchelle24@gmail.com</t>
-        </is>
-      </c>
-      <c r="D810" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>Hannah</t>
-        </is>
-      </c>
-      <c r="B811" t="inlineStr">
-        <is>
-          <t>Hackney</t>
-        </is>
-      </c>
-      <c r="C811" t="inlineStr">
-        <is>
-          <t>emilyhackney014@gmail.com</t>
-        </is>
-      </c>
-      <c r="D811" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="B812" t="inlineStr">
-        <is>
-          <t>Zaidan</t>
-        </is>
-      </c>
-      <c r="C812" t="inlineStr">
-        <is>
-          <t>aliziadan@gmail.com</t>
-        </is>
-      </c>
-      <c r="D812" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>Thea</t>
-        </is>
-      </c>
-      <c r="B813" t="inlineStr">
-        <is>
-          <t>Stewart-Carter</t>
-        </is>
-      </c>
-      <c r="C813" t="inlineStr">
-        <is>
-          <t>misssprim@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>Joyce</t>
-        </is>
-      </c>
-      <c r="B814" t="inlineStr">
-        <is>
-          <t>Villegas</t>
-        </is>
-      </c>
-      <c r="C814" t="inlineStr">
-        <is>
-          <t>joycevillegas0425@gmail.com</t>
-        </is>
-      </c>
-      <c r="D814" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>Nevjot</t>
-        </is>
-      </c>
-      <c r="B815" t="inlineStr">
-        <is>
-          <t>Kaur</t>
-        </is>
-      </c>
-      <c r="C815" t="inlineStr">
-        <is>
-          <t>97kaurnevjot@gmail.com</t>
-        </is>
-      </c>
-      <c r="D815" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>Victor</t>
-        </is>
-      </c>
-      <c r="B816" t="inlineStr">
-        <is>
-          <t>Savic</t>
-        </is>
-      </c>
-      <c r="C816" t="inlineStr">
-        <is>
-          <t>victorsavic50@gmail.com</t>
-        </is>
-      </c>
-      <c r="D816" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>Liam</t>
-        </is>
-      </c>
-      <c r="B817" t="inlineStr">
-        <is>
-          <t>Duggan</t>
-        </is>
-      </c>
-      <c r="C817" t="inlineStr">
-        <is>
-          <t>liamduggan543@gmail.com</t>
-        </is>
-      </c>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>Abishek</t>
-        </is>
-      </c>
-      <c r="B818" t="inlineStr">
-        <is>
-          <t>bhandari</t>
-        </is>
-      </c>
-      <c r="C818" t="inlineStr">
-        <is>
-          <t>bhandariabishek55@gmail.com</t>
-        </is>
-      </c>
-      <c r="D818" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>harnek</t>
-        </is>
-      </c>
-      <c r="B819" t="inlineStr">
-        <is>
-          <t>singh</t>
-        </is>
-      </c>
-      <c r="C819" t="inlineStr">
-        <is>
-          <t>harneksinghhoney123@gmail.com</t>
-        </is>
-      </c>
-      <c r="D819" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="B820" t="inlineStr">
-        <is>
-          <t>Fontaine</t>
-        </is>
-      </c>
-      <c r="C820" t="inlineStr">
-        <is>
-          <t>nicoel.fontaine@everythingccs.com</t>
-        </is>
-      </c>
-      <c r="D820" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>Tina</t>
-        </is>
-      </c>
-      <c r="B821" t="inlineStr">
-        <is>
-          <t>Fiumenero</t>
-        </is>
-      </c>
-      <c r="C821" t="inlineStr">
-        <is>
-          <t>tinafiumenero@aol.com</t>
-        </is>
-      </c>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>Daniella</t>
-        </is>
-      </c>
-      <c r="B822" t="inlineStr">
-        <is>
-          <t>Church</t>
-        </is>
-      </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t>daniella_24@icloud.com</t>
-        </is>
-      </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>Lisa</t>
-        </is>
-      </c>
-      <c r="B823" t="inlineStr">
-        <is>
-          <t>Sims</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>ljrsims@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" t="inlineStr">
-        <is>
-          <t>Beth</t>
-        </is>
-      </c>
-      <c r="B824" t="inlineStr">
-        <is>
-          <t>Reurink</t>
-        </is>
-      </c>
-      <c r="C824" t="inlineStr">
-        <is>
-          <t>breurink@gmail.com</t>
-        </is>
-      </c>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" t="inlineStr">
-        <is>
-          <t>Fernanda</t>
-        </is>
-      </c>
-      <c r="B825" t="inlineStr">
-        <is>
-          <t>Oakes</t>
-        </is>
-      </c>
-      <c r="C825" t="inlineStr">
-        <is>
-          <t>oakesfernanda@gmail.com</t>
-        </is>
-      </c>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" t="inlineStr">
-        <is>
-          <t>Barb</t>
-        </is>
-      </c>
-      <c r="B826" t="inlineStr">
-        <is>
-          <t>Prince</t>
-        </is>
-      </c>
-      <c r="C826" t="inlineStr">
-        <is>
-          <t>bprince10@icloud.com</t>
-        </is>
-      </c>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" t="inlineStr">
-        <is>
-          <t>Parthkumar</t>
-        </is>
-      </c>
-      <c r="B827" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C827" t="inlineStr">
-        <is>
-          <t>parth.patel@valianttms.com</t>
-        </is>
-      </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" t="inlineStr">
-        <is>
-          <t>Kathleen</t>
-        </is>
-      </c>
-      <c r="B828" t="inlineStr">
-        <is>
-          <t>Ake</t>
-        </is>
-      </c>
-      <c r="C828" t="inlineStr">
-        <is>
-          <t>kathleenake1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" t="inlineStr">
-        <is>
-          <t>Tyler</t>
-        </is>
-      </c>
-      <c r="B829" t="inlineStr">
-        <is>
-          <t>Kettlewell</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr">
-        <is>
-          <t>tyketts27@gmail.com</t>
-        </is>
-      </c>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>Goran</t>
-        </is>
-      </c>
-      <c r="B830" t="inlineStr">
-        <is>
-          <t>Jamina</t>
-        </is>
-      </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>gjamina63@gmail.com</t>
-        </is>
-      </c>
-      <c r="D830" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>Jasmina</t>
-        </is>
-      </c>
-      <c r="B831" t="inlineStr">
-        <is>
-          <t>Kaye</t>
-        </is>
-      </c>
-      <c r="C831" t="inlineStr">
-        <is>
-          <t>kayejasmin7@gmail.com</t>
-        </is>
-      </c>
-      <c r="D831" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>Adrianna</t>
-        </is>
-      </c>
-      <c r="B832" t="inlineStr">
-        <is>
-          <t>Faubert</t>
-        </is>
-      </c>
-      <c r="C832" t="inlineStr">
-        <is>
-          <t>adriannafaubert1001@gmail.com</t>
-        </is>
-      </c>
-      <c r="D832" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="inlineStr">
-        <is>
-          <t>Cedrik</t>
-        </is>
-      </c>
-      <c r="B833" t="inlineStr">
-        <is>
-          <t>Cabana</t>
-        </is>
-      </c>
-      <c r="C833" t="inlineStr">
-        <is>
-          <t>ccabana@hockeycanada.ca</t>
-        </is>
-      </c>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
-        <is>
-          <t>Emma</t>
-        </is>
-      </c>
-      <c r="B834" t="inlineStr">
-        <is>
-          <t>Manera</t>
-        </is>
-      </c>
-      <c r="C834" t="inlineStr">
-        <is>
-          <t>emmarberg5@gmail.com</t>
-        </is>
-      </c>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>Morgenstern</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>rjmstern2@gmail.com</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>Lucca</t>
-        </is>
-      </c>
-      <c r="B836" t="inlineStr">
-        <is>
-          <t>Trajkovski</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr">
-        <is>
-          <t>luccatrajovski@gmail.com</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="B837" t="inlineStr">
-        <is>
-          <t>Kabbani</t>
-        </is>
-      </c>
-      <c r="C837" t="inlineStr">
-        <is>
-          <t>ali.kabbani@everythingccs.com</t>
-        </is>
-      </c>
-      <c r="D837" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" t="inlineStr">
-        <is>
-          <t>Mason</t>
-        </is>
-      </c>
-      <c r="B838" t="inlineStr">
-        <is>
-          <t>Connor</t>
-        </is>
-      </c>
-      <c r="C838" t="inlineStr"/>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>Ky</t>
-        </is>
-      </c>
-      <c r="B839" t="inlineStr">
-        <is>
-          <t>Patrick</t>
-        </is>
-      </c>
-      <c r="C839" t="inlineStr">
-        <is>
-          <t>kyron.patrick@everythingccs.com</t>
-        </is>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" t="inlineStr">
-        <is>
-          <t>Logan</t>
-        </is>
-      </c>
-      <c r="B840" t="inlineStr">
-        <is>
-          <t>Deneau</t>
-        </is>
-      </c>
-      <c r="C840" t="inlineStr">
-        <is>
-          <t>logandeneau@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
-      <c r="B841" t="inlineStr">
-        <is>
-          <t>Dougherty</t>
-        </is>
-      </c>
-      <c r="C841" t="inlineStr">
-        <is>
-          <t>michael.dougherty@everythingccs.com</t>
-        </is>
-      </c>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>Ruth</t>
-        </is>
-      </c>
-      <c r="B842" t="inlineStr">
-        <is>
-          <t>McGhee</t>
-        </is>
-      </c>
-      <c r="C842" t="inlineStr">
-        <is>
-          <t>ruthmcghee08@gmail.com</t>
-        </is>
-      </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" t="inlineStr">
-        <is>
-          <t>Dave</t>
-        </is>
-      </c>
-      <c r="B843" t="inlineStr">
-        <is>
-          <t>Connor</t>
-        </is>
-      </c>
-      <c r="C843" t="inlineStr">
-        <is>
-          <t>conndave83@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" t="inlineStr">
-        <is>
-          <t>Kayla</t>
-        </is>
-      </c>
-      <c r="B844" t="inlineStr">
-        <is>
-          <t>DiSchiavo</t>
-        </is>
-      </c>
-      <c r="C844" t="inlineStr">
-        <is>
-          <t>kayla.dischiavo@everythingccs.com</t>
-        </is>
-      </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="B845" t="inlineStr">
-        <is>
-          <t>Duren</t>
-        </is>
-      </c>
-      <c r="C845" t="inlineStr">
-        <is>
-          <t>tinyduren@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="846">
-      <c r="A846" t="inlineStr">
-        <is>
-          <t>Xavier</t>
-        </is>
-      </c>
-      <c r="B846" t="inlineStr">
-        <is>
-          <t>seguin</t>
-        </is>
-      </c>
-      <c r="C846" t="inlineStr">
-        <is>
-          <t>xaviercseguin@gmail.com</t>
-        </is>
-      </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" t="inlineStr">
-        <is>
-          <t>Kennedy</t>
-        </is>
-      </c>
-      <c r="B847" t="inlineStr">
-        <is>
-          <t>Connor</t>
-        </is>
-      </c>
-      <c r="C847" t="inlineStr"/>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="848">
-      <c r="A848" t="inlineStr">
-        <is>
-          <t>Huli</t>
-        </is>
-      </c>
-      <c r="B848" t="inlineStr">
-        <is>
-          <t>Bokure</t>
-        </is>
-      </c>
-      <c r="C848" t="inlineStr">
-        <is>
-          <t>huldi.mebrahtu@gmail.com</t>
-        </is>
-      </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" t="inlineStr">
-        <is>
-          <t>Mackenzie</t>
-        </is>
-      </c>
-      <c r="B849" t="inlineStr">
-        <is>
-          <t>Doucette</t>
-        </is>
-      </c>
-      <c r="C849" t="inlineStr">
-        <is>
-          <t>mackenzie.doucette@everythingccs.com</t>
-        </is>
-      </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="850">
-      <c r="A850" t="inlineStr">
-        <is>
-          <t>Daniella</t>
-        </is>
-      </c>
-      <c r="B850" t="inlineStr">
-        <is>
-          <t>Church</t>
-        </is>
-      </c>
-      <c r="C850" t="inlineStr">
-        <is>
-          <t>daniella.church1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" t="inlineStr">
-        <is>
-          <t>Elizabeth</t>
-        </is>
-      </c>
-      <c r="B851" t="inlineStr">
-        <is>
-          <t>Monroy</t>
-        </is>
-      </c>
-      <c r="C851" t="inlineStr"/>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="852">
-      <c r="A852" t="inlineStr">
-        <is>
-          <t>Jax</t>
-        </is>
-      </c>
-      <c r="B852" t="inlineStr">
-        <is>
-          <t>Wasilewski</t>
-        </is>
-      </c>
-      <c r="C852" t="inlineStr"/>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="853">
-      <c r="A853" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="B853" t="inlineStr">
-        <is>
-          <t>Monroy</t>
-        </is>
-      </c>
-      <c r="C853" t="inlineStr"/>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="B854" t="inlineStr">
-        <is>
-          <t>Vargas</t>
-        </is>
-      </c>
-      <c r="C854" t="inlineStr">
-        <is>
-          <t>haidevars20@gmail.com</t>
-        </is>
-      </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="855">
-      <c r="A855" t="inlineStr">
-        <is>
-          <t>Noah</t>
-        </is>
-      </c>
-      <c r="B855" t="inlineStr">
-        <is>
-          <t>Cherian</t>
-        </is>
-      </c>
-      <c r="C855" t="inlineStr">
-        <is>
-          <t>noahcherian@icloud.com</t>
-        </is>
-      </c>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="856">
-      <c r="A856" t="inlineStr">
-        <is>
-          <t>Fernanda</t>
-        </is>
-      </c>
-      <c r="B856" t="inlineStr">
-        <is>
-          <t>Rivera</t>
-        </is>
-      </c>
-      <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="857">
-      <c r="A857" t="inlineStr">
-        <is>
-          <t>Katelyn</t>
-        </is>
-      </c>
-      <c r="B857" t="inlineStr">
-        <is>
-          <t>McMahon</t>
-        </is>
-      </c>
-      <c r="C857" t="inlineStr">
-        <is>
-          <t>katelyn@lakeland-homes.ca</t>
-        </is>
-      </c>
-      <c r="D857" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="858">
-      <c r="A858" t="inlineStr">
-        <is>
-          <t>Sergio</t>
-        </is>
-      </c>
-      <c r="B858" t="inlineStr">
-        <is>
-          <t>Zamudio</t>
-        </is>
-      </c>
-      <c r="C858" t="inlineStr">
-        <is>
-          <t>antmonmen@gmail.com</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="859">
-      <c r="A859" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="B859" t="inlineStr">
-        <is>
-          <t>Rivera</t>
-        </is>
-      </c>
-      <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="860">
-      <c r="A860" t="inlineStr">
-        <is>
-          <t>Julianne</t>
-        </is>
-      </c>
-      <c r="B860" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C860" t="inlineStr">
-        <is>
-          <t>22jewls@gmail.com</t>
-        </is>
-      </c>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="861">
-      <c r="A861" t="inlineStr">
-        <is>
-          <t>Aleah</t>
-        </is>
-      </c>
-      <c r="B861" t="inlineStr">
-        <is>
-          <t>Wasilewski</t>
-        </is>
-      </c>
-      <c r="C861" t="inlineStr"/>
-      <c r="D861" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="862">
-      <c r="A862" t="inlineStr">
-        <is>
-          <t>Tina</t>
-        </is>
-      </c>
-      <c r="B862" t="inlineStr">
-        <is>
-          <t>Sauro</t>
-        </is>
-      </c>
-      <c r="C862" t="inlineStr"/>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="863">
-      <c r="A863" t="inlineStr">
-        <is>
-          <t>Moh</t>
-        </is>
-      </c>
-      <c r="B863" t="inlineStr">
-        <is>
-          <t>Haidous</t>
-        </is>
-      </c>
-      <c r="C863" t="inlineStr">
-        <is>
-          <t>mohahidous@gmail.com</t>
-        </is>
-      </c>
-      <c r="D863" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="864">
-      <c r="A864" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
-      <c r="B864" t="inlineStr">
-        <is>
-          <t>Wasilewski</t>
-        </is>
-      </c>
-      <c r="C864" t="inlineStr">
-        <is>
-          <t>mikewasi@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D864" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="865">
-      <c r="A865" t="inlineStr">
-        <is>
-          <t>Brielle</t>
-        </is>
-      </c>
-      <c r="B865" t="inlineStr">
-        <is>
-          <t>Loebach</t>
-        </is>
-      </c>
-      <c r="C865" t="inlineStr">
-        <is>
-          <t>brielle.loebach@gmail.com</t>
-        </is>
-      </c>
-      <c r="D865" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="866">
-      <c r="A866" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="B866" t="inlineStr">
-        <is>
-          <t>Lott</t>
-        </is>
-      </c>
-      <c r="C866" t="inlineStr">
-        <is>
-          <t>jackpd16@gmail.com</t>
-        </is>
-      </c>
-      <c r="D866" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="867">
-      <c r="A867" t="inlineStr">
-        <is>
-          <t>Jayden</t>
-        </is>
-      </c>
-      <c r="B867" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="C867" t="inlineStr">
-        <is>
-          <t>jayden.toulouse@gmail.com</t>
-        </is>
-      </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="868">
-      <c r="A868" t="inlineStr">
-        <is>
-          <t>Kaelyn</t>
-        </is>
-      </c>
-      <c r="B868" t="inlineStr">
-        <is>
-          <t>Soanes</t>
-        </is>
-      </c>
-      <c r="C868" t="inlineStr">
-        <is>
-          <t>kaelynsoanes@gmail.com</t>
-        </is>
-      </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>Melissa</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr">
-        <is>
-          <t>Lafreniere</t>
-        </is>
-      </c>
-      <c r="C869" t="inlineStr">
-        <is>
-          <t>mlafreniere1225@gmail.com</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>Evan</t>
-        </is>
-      </c>
-      <c r="B870" t="inlineStr">
-        <is>
-          <t>Heath</t>
-        </is>
-      </c>
-      <c r="C870" t="inlineStr">
-        <is>
-          <t>evan.a.heath@gmail.com</t>
-        </is>
-      </c>
-      <c r="D870" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B871" t="inlineStr">
-        <is>
-          <t>Mancini</t>
-        </is>
-      </c>
-      <c r="C871" t="inlineStr">
-        <is>
-          <t>paul.c.mancini@gmail.com</t>
-        </is>
-      </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="872">
-      <c r="A872" t="inlineStr">
-        <is>
-          <t>Emilie</t>
-        </is>
-      </c>
-      <c r="B872" t="inlineStr">
-        <is>
-          <t>Holjevac</t>
-        </is>
-      </c>
-      <c r="C872" t="inlineStr">
-        <is>
-          <t>holjevacemilie@gmail.com</t>
-        </is>
-      </c>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="873">
-      <c r="A873" t="inlineStr">
-        <is>
-          <t>Eric</t>
-        </is>
-      </c>
-      <c r="B873" t="inlineStr">
-        <is>
-          <t>Burningham</t>
-        </is>
-      </c>
-      <c r="C873" t="inlineStr">
-        <is>
-          <t>ericmark2009@gmail.com</t>
-        </is>
-      </c>
-      <c r="D873" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="874">
-      <c r="A874" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="B874" t="inlineStr">
-        <is>
-          <t>Renon</t>
-        </is>
-      </c>
-      <c r="C874" t="inlineStr">
-        <is>
-          <t>andrew.renon08@gmail.com</t>
-        </is>
-      </c>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="875">
-      <c r="A875" t="inlineStr">
-        <is>
-          <t>Jacob</t>
-        </is>
-      </c>
-      <c r="B875" t="inlineStr">
-        <is>
-          <t>Dupree</t>
-        </is>
-      </c>
-      <c r="C875" t="inlineStr">
-        <is>
-          <t>jacobdupree890@gmail.com</t>
-        </is>
-      </c>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="876">
-      <c r="A876" t="inlineStr">
-        <is>
-          <t>mario</t>
-        </is>
-      </c>
-      <c r="B876" t="inlineStr">
-        <is>
-          <t>Ruggirello</t>
-        </is>
-      </c>
-      <c r="C876" t="inlineStr">
-        <is>
-          <t>marioruggirello@gmail.com</t>
-        </is>
-      </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>Calvin</t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t>Grondin</t>
-        </is>
-      </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t>calvingrondin@yahoo.com</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="B878" t="inlineStr">
-        <is>
-          <t>Barei</t>
-        </is>
-      </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t>savannahbarei02@icloud.com</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>Syed</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t>Rayan</t>
-        </is>
-      </c>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t>srayan7107@gmail.com</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" t="inlineStr">
-        <is>
-          <t>Marie</t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr">
-        <is>
-          <t>Keresztyen</t>
-        </is>
-      </c>
-      <c r="C880" t="inlineStr">
-        <is>
-          <t>mkrezjen@gmail.com</t>
-        </is>
-      </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="881">
-      <c r="A881" t="inlineStr">
-        <is>
-          <t>alessia</t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr">
-        <is>
-          <t>carlesimo</t>
-        </is>
-      </c>
-      <c r="C881" t="inlineStr">
-        <is>
-          <t>alessia.carlesimo@mytools2go.ca</t>
-        </is>
-      </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr">
-        <is>
-          <t>Hodare</t>
-        </is>
-      </c>
-      <c r="C882" t="inlineStr">
-        <is>
-          <t>shodare5@gmail.com</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t>Wiktoria</t>
-        </is>
-      </c>
-      <c r="B883" t="inlineStr">
-        <is>
-          <t>Hartung</t>
-        </is>
-      </c>
-      <c r="C883" t="inlineStr">
-        <is>
-          <t>wiktoriaha7@gmail.com</t>
-        </is>
-      </c>
-      <c r="D883" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" t="inlineStr">
-        <is>
-          <t>Bella</t>
-        </is>
-      </c>
-      <c r="B884" t="inlineStr">
-        <is>
-          <t>Rosenkranz-krausse</t>
-        </is>
-      </c>
-      <c r="C884" t="inlineStr">
-        <is>
-          <t>bellarosenkrausse@gmail.com</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" t="inlineStr">
-        <is>
-          <t>Gabriella</t>
-        </is>
-      </c>
-      <c r="B885" t="inlineStr">
-        <is>
-          <t>Agostino</t>
-        </is>
-      </c>
-      <c r="C885" t="inlineStr">
-        <is>
-          <t>gabriella.agostino2@gmail.com</t>
-        </is>
-      </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="886">
-      <c r="A886" t="inlineStr">
-        <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="B886" t="inlineStr">
-        <is>
-          <t>Armstrong</t>
-        </is>
-      </c>
-      <c r="C886" t="inlineStr">
-        <is>
-          <t>fazekasg@uwindsor.ca</t>
-        </is>
-      </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="887">
-      <c r="A887" t="inlineStr">
-        <is>
-          <t>Puneet</t>
-        </is>
-      </c>
-      <c r="B887" t="inlineStr">
-        <is>
-          <t>Gupta</t>
-        </is>
-      </c>
-      <c r="C887" t="inlineStr">
-        <is>
-          <t>72-backups.modest@icloud.com</t>
-        </is>
-      </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="888">
-      <c r="A888" t="inlineStr">
-        <is>
-          <t>Joe</t>
-        </is>
-      </c>
-      <c r="B888" t="inlineStr">
-        <is>
-          <t>Saddy</t>
-        </is>
-      </c>
-      <c r="C888" t="inlineStr">
-        <is>
-          <t>saddyjoey@gmail.com</t>
-        </is>
-      </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="889">
-      <c r="A889" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="B889" t="inlineStr">
-        <is>
-          <t>Meret</t>
-        </is>
-      </c>
-      <c r="C889" t="inlineStr">
-        <is>
-          <t>meretmichelle@gmail.com</t>
-        </is>
-      </c>
-      <c r="D889" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="890">
-      <c r="A890" t="inlineStr">
-        <is>
-          <t>Nina</t>
-        </is>
-      </c>
-      <c r="B890" t="inlineStr">
-        <is>
-          <t>Lue Pann</t>
-        </is>
-      </c>
-      <c r="C890" t="inlineStr">
-        <is>
-          <t>nmluepann@gmail.com</t>
-        </is>
-      </c>
-      <c r="D890" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="891">
-      <c r="A891" t="inlineStr">
-        <is>
-          <t>Alyssa</t>
-        </is>
-      </c>
-      <c r="B891" t="inlineStr">
-        <is>
-          <t>Layfield</t>
-        </is>
-      </c>
-      <c r="C891" t="inlineStr">
-        <is>
-          <t>alyssasleiman@gmail.com</t>
-        </is>
-      </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="892">
-      <c r="A892" t="inlineStr">
-        <is>
-          <t>Ibrahim</t>
-        </is>
-      </c>
-      <c r="B892" t="inlineStr">
-        <is>
-          <t>Amezyane</t>
-        </is>
-      </c>
-      <c r="C892" t="inlineStr">
-        <is>
-          <t>ibramezyane@gmail.com</t>
-        </is>
-      </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="893">
-      <c r="A893" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="B893" t="inlineStr">
-        <is>
-          <t>Mancini</t>
-        </is>
-      </c>
-      <c r="C893" t="inlineStr">
-        <is>
-          <t>charlie.mancini@mytools2go.ca</t>
-        </is>
-      </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="894">
-      <c r="A894" t="inlineStr">
-        <is>
-          <t>Stuart</t>
-        </is>
-      </c>
-      <c r="B894" t="inlineStr">
-        <is>
-          <t>Anderson</t>
-        </is>
-      </c>
-      <c r="C894" t="inlineStr">
-        <is>
-          <t>stewanderson@protonmail.com</t>
-        </is>
-      </c>
-      <c r="D894" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="895">
-      <c r="A895" t="inlineStr">
-        <is>
-          <t>Saarth</t>
-        </is>
-      </c>
-      <c r="B895" t="inlineStr">
-        <is>
-          <t>Desai</t>
-        </is>
-      </c>
-      <c r="C895" t="inlineStr">
-        <is>
-          <t>saarth.desai@gmail.com</t>
-        </is>
-      </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="896">
-      <c r="A896" t="inlineStr">
-        <is>
-          <t>Rishab</t>
-        </is>
-      </c>
-      <c r="B896" t="inlineStr">
-        <is>
-          <t>Reen</t>
-        </is>
-      </c>
-      <c r="C896" t="inlineStr">
-        <is>
-          <t>rishabreen@gmail.com</t>
-        </is>
-      </c>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="897">
-      <c r="A897" t="inlineStr">
-        <is>
-          <t>Rahul</t>
-        </is>
-      </c>
-      <c r="B897" t="inlineStr">
-        <is>
-          <t>Madaan</t>
-        </is>
-      </c>
-      <c r="C897" t="inlineStr">
-        <is>
-          <t>rahulmadaan5464@gmail.com</t>
-        </is>
-      </c>
-      <c r="D897" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="898">
-      <c r="A898" t="inlineStr">
-        <is>
-          <t>Ramon</t>
-        </is>
-      </c>
-      <c r="B898" t="inlineStr">
-        <is>
-          <t>Salvador</t>
-        </is>
-      </c>
-      <c r="C898" t="inlineStr">
-        <is>
-          <t>salvador.ramon6@gmail.com</t>
-        </is>
-      </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="899">
-      <c r="A899" t="inlineStr">
-        <is>
-          <t>Macaelle Ricci</t>
-        </is>
-      </c>
-      <c r="B899" t="inlineStr">
-        <is>
-          <t>Salvador</t>
-        </is>
-      </c>
-      <c r="C899" t="inlineStr"/>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="900">
-      <c r="A900" t="inlineStr">
-        <is>
-          <t>Mohammed</t>
-        </is>
-      </c>
-      <c r="B900" t="inlineStr">
-        <is>
-          <t>Koumaneh</t>
-        </is>
-      </c>
-      <c r="C900" t="inlineStr">
-        <is>
-          <t>koumaneh3434@gmail.com</t>
-        </is>
-      </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="901">
-      <c r="A901" t="inlineStr">
-        <is>
-          <t>Ganapathy</t>
-        </is>
-      </c>
-      <c r="B901" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="C901" t="inlineStr">
-        <is>
-          <t>ganapathy.raman@gmail.com</t>
-        </is>
-      </c>
-      <c r="D901" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="902">
-      <c r="A902" t="inlineStr">
-        <is>
-          <t>Calista</t>
-        </is>
-      </c>
-      <c r="B902" t="inlineStr">
-        <is>
-          <t>Belekoukias</t>
-        </is>
-      </c>
-      <c r="C902" t="inlineStr">
-        <is>
-          <t>belekoukiasc@gmail.com</t>
-        </is>
-      </c>
-      <c r="D902" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="903">
-      <c r="A903" t="inlineStr">
-        <is>
-          <t>Chael Sebastian</t>
-        </is>
-      </c>
-      <c r="B903" t="inlineStr">
-        <is>
-          <t>Salvador</t>
-        </is>
-      </c>
-      <c r="C903" t="inlineStr"/>
-      <c r="D903" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="904">
-      <c r="A904" t="inlineStr">
-        <is>
-          <t>Charmaine</t>
-        </is>
-      </c>
-      <c r="B904" t="inlineStr">
-        <is>
-          <t>Salvador</t>
-        </is>
-      </c>
-      <c r="C904" t="inlineStr"/>
-      <c r="D904" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="905">
-      <c r="A905" t="inlineStr">
-        <is>
-          <t>Kathryn</t>
-        </is>
-      </c>
-      <c r="B905" t="inlineStr">
-        <is>
-          <t>Collins</t>
-        </is>
-      </c>
-      <c r="C905" t="inlineStr">
-        <is>
-          <t>kathcollins67@gmail.com</t>
-        </is>
-      </c>
-      <c r="D905" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="906">
-      <c r="A906" t="inlineStr">
-        <is>
-          <t>Aash</t>
-        </is>
-      </c>
-      <c r="B906" t="inlineStr">
-        <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="C906" t="inlineStr">
-        <is>
-          <t>richard.aash81@gmail.com</t>
-        </is>
-      </c>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="907">
-      <c r="A907" t="inlineStr">
-        <is>
-          <t>adam</t>
-        </is>
-      </c>
-      <c r="B907" t="inlineStr">
-        <is>
-          <t>bisson</t>
-        </is>
-      </c>
-      <c r="C907" t="inlineStr">
-        <is>
-          <t>adambison@pickleplex.ca</t>
-        </is>
-      </c>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="908">
-      <c r="A908" t="inlineStr">
-        <is>
-          <t>Meet</t>
-        </is>
-      </c>
-      <c r="B908" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C908" t="inlineStr">
-        <is>
-          <t>meetpatel@nextstar-energy.com</t>
-        </is>
-      </c>
-      <c r="D908" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="909">
-      <c r="A909" t="inlineStr">
-        <is>
-          <t>J-P</t>
-        </is>
-      </c>
-      <c r="B909" t="inlineStr">
-        <is>
-          <t>Girard</t>
-        </is>
-      </c>
-      <c r="C909" t="inlineStr">
-        <is>
-          <t>jpgirard307@gmail.com</t>
-        </is>
-      </c>
-      <c r="D909" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="910">
-      <c r="A910" t="inlineStr">
-        <is>
-          <t>Conrad</t>
-        </is>
-      </c>
-      <c r="B910" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C910" t="inlineStr">
-        <is>
-          <t>conrad12gabriel@gmail.com</t>
-        </is>
-      </c>
-      <c r="D910" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="911">
-      <c r="A911" t="inlineStr">
-        <is>
-          <t>Shobha</t>
-        </is>
-      </c>
-      <c r="B911" t="inlineStr">
-        <is>
-          <t>Chandrashekhar</t>
-        </is>
-      </c>
-      <c r="C911" t="inlineStr">
-        <is>
-          <t>shobhac59@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="912">
-      <c r="A912" t="inlineStr">
-        <is>
-          <t>Todd</t>
-        </is>
-      </c>
-      <c r="B912" t="inlineStr">
-        <is>
-          <t>Krauss</t>
-        </is>
-      </c>
-      <c r="C912" t="inlineStr">
-        <is>
-          <t>todd@kraussfamily.ca</t>
-        </is>
-      </c>
-      <c r="D912" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="913">
-      <c r="A913" t="inlineStr">
-        <is>
-          <t>Chandra</t>
-        </is>
-      </c>
-      <c r="B913" t="inlineStr">
-        <is>
-          <t>Shekhar</t>
-        </is>
-      </c>
-      <c r="C913" t="inlineStr">
-        <is>
-          <t>shekharc54@gmail.com</t>
-        </is>
-      </c>
-      <c r="D913" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="914">
-      <c r="A914" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="B914" t="inlineStr">
-        <is>
-          <t>Del Ciancio</t>
-        </is>
-      </c>
-      <c r="C914" t="inlineStr">
-        <is>
-          <t>charliedelciancio@gmail.com</t>
-        </is>
-      </c>
-      <c r="D914" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="915">
-      <c r="A915" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="B915" t="inlineStr">
-        <is>
-          <t>Del Ciancio</t>
-        </is>
-      </c>
-      <c r="C915" t="inlineStr">
-        <is>
-          <t>maxdelciancio@gmail.com</t>
-        </is>
-      </c>
-      <c r="D915" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr">
-        <is>
-          <t>Steven</t>
-        </is>
-      </c>
-      <c r="B916" t="inlineStr">
-        <is>
-          <t>Andrade</t>
-        </is>
-      </c>
-      <c r="C916" t="inlineStr">
-        <is>
-          <t>steven_andrade8@outlook.com</t>
-        </is>
-      </c>
-      <c r="D916" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="917">
-      <c r="A917" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
-      <c r="B917" t="inlineStr">
-        <is>
-          <t>Pullano</t>
-        </is>
-      </c>
-      <c r="C917" t="inlineStr">
-        <is>
-          <t>mpullano123@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D917" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="918">
-      <c r="A918" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="B918" t="inlineStr">
-        <is>
-          <t>Del Ciancio</t>
-        </is>
-      </c>
-      <c r="C918" t="inlineStr">
-        <is>
-          <t>jackdelciancio@gmail.com</t>
-        </is>
-      </c>
-      <c r="D918" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="919">
-      <c r="A919" t="inlineStr">
-        <is>
-          <t>Jacqueline</t>
-        </is>
-      </c>
-      <c r="B919" t="inlineStr">
-        <is>
-          <t>Gatecliff</t>
-        </is>
-      </c>
-      <c r="C919" t="inlineStr">
-        <is>
-          <t>jgatecliff33@gmail.com</t>
-        </is>
-      </c>
-      <c r="D919" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="920">
-      <c r="A920" t="inlineStr">
-        <is>
-          <t>Taisija</t>
-        </is>
-      </c>
-      <c r="B920" t="inlineStr">
-        <is>
-          <t>Slobodjabova</t>
-        </is>
-      </c>
-      <c r="C920" t="inlineStr">
-        <is>
-          <t>taisija.slobodjanova@gmail.com</t>
-        </is>
-      </c>
-      <c r="D920" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="921">
-      <c r="A921" t="inlineStr">
-        <is>
-          <t>Tautvydas</t>
-        </is>
-      </c>
-      <c r="B921" t="inlineStr">
-        <is>
-          <t>Jamantas</t>
-        </is>
-      </c>
-      <c r="C921" t="inlineStr">
-        <is>
-          <t>tautvydas.jotvingas@gmail.com</t>
-        </is>
-      </c>
-      <c r="D921" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr">
-        <is>
-          <t>Valeria</t>
-        </is>
-      </c>
-      <c r="B922" t="inlineStr">
-        <is>
-          <t>Roldan</t>
-        </is>
-      </c>
-      <c r="C922" t="inlineStr">
-        <is>
-          <t>karinaroldan.119@gmail.com</t>
-        </is>
-      </c>
-      <c r="D922" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B923" t="inlineStr">
-        <is>
-          <t>Bahnam</t>
-        </is>
-      </c>
-      <c r="C923" t="inlineStr">
-        <is>
-          <t>pbahnam@uwo.ca</t>
-        </is>
-      </c>
-      <c r="D923" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr">
-        <is>
-          <t>Poppy</t>
-        </is>
-      </c>
-      <c r="B924" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="C924" t="inlineStr">
-        <is>
-          <t>poppybennett20@gmail.com</t>
-        </is>
-      </c>
-      <c r="D924" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr">
-        <is>
-          <t>Ashish</t>
-        </is>
-      </c>
-      <c r="B925" t="inlineStr">
-        <is>
-          <t>Anbasti</t>
-        </is>
-      </c>
-      <c r="C925" t="inlineStr">
-        <is>
-          <t>anbasti0091@gmail.com</t>
-        </is>
-      </c>
-      <c r="D925" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr">
-        <is>
-          <t>Hamza</t>
-        </is>
-      </c>
-      <c r="B926" t="inlineStr">
-        <is>
-          <t>Nebili</t>
-        </is>
-      </c>
-      <c r="C926" t="inlineStr">
-        <is>
-          <t>hamzanebili3001@gmail.com</t>
-        </is>
-      </c>
-      <c r="D926" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr">
-        <is>
-          <t>Ashish</t>
-        </is>
-      </c>
-      <c r="B927" t="inlineStr">
-        <is>
-          <t>Anbasti</t>
-        </is>
-      </c>
-      <c r="C927" t="inlineStr">
-        <is>
-          <t>ashisha.8470@gmail.com</t>
-        </is>
-      </c>
-      <c r="D927" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr">
-        <is>
-          <t>Geoffrey</t>
-        </is>
-      </c>
-      <c r="B928" t="inlineStr">
-        <is>
-          <t>MacNeil</t>
-        </is>
-      </c>
-      <c r="C928" t="inlineStr">
-        <is>
-          <t>geoffreymacneil3@gmaikl.com</t>
-        </is>
-      </c>
-      <c r="D928" t="inlineStr">
-        <is>
-          <t>windsor@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr">
-        <is>
-          <t>Xinyun</t>
-        </is>
-      </c>
-      <c r="B929" t="inlineStr">
-        <is>
-          <t>He</t>
-        </is>
-      </c>
-      <c r="C929" t="inlineStr">
-        <is>
-          <t>1431266138@qq.com</t>
-        </is>
-      </c>
-      <c r="D929" t="inlineStr">
         <is>
           <t>windsor@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Windsor.xlsx
+++ b/docs/downloads/Windsor.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D754"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14340,6 +14340,1452 @@
         </is>
       </c>
     </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>reema</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>ray</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>rayreema@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Khao-one</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>ckhaoon1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Marisa</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Lunghi</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>marisalu1330@gmail.com</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Luu</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>johnsonluu_2002@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Katrina</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Tarcia</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>ketarcia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Iztli</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Galde</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>iztlicanada@gmail.com</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Meenakshi</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Bhatia</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Zeboony</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>azeboony@gmail.com</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Cannon</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>owencannon124@gmail.com</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Imperioli</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>imperioli@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Gallant</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>004.beccajagallant@gmail.com</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Petrilli</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>michaelp13131313@gmail.com</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Petrilli</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>fapetrilli@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Kada</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Malek</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>mcsah3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Ryu H</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Thien</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Dang</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>thien.dang336@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Keng</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Ferrato</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>cferrato1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Ferrato</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>peterferrato@hallergroup.ca</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>ahsen</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>mangal</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>mangal1@uwindsor.ca</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Hat</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Le</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>hatlvh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Mgiizi</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>wrightmgiizi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Isaiah</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Maracle</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>isaiahmaracle23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Mahlet</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Teka</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>mteka@newbe.ca</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Bishara</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Qare</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>bisharaq@outlook.com</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Keira</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Sword</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>swordkeira@gmail.com</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Lovish</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Kanda</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>lovishkanda99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Ariton</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Bushi</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>abushi@newbe.ca</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Gabby</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Pildner</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>gabby327@comcast.net</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Yim</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>connoryim@gmail.com</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>GOODWIN</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>heatherjgoodwin@outlook.com</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Kaylen</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>kaylenwilliams63@gmail.com</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Mariam</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Hammoud</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>mariam.hammoud3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Mallory</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>mallory_morgan@live.ca</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Reza</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Sadeghi</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>r.m.s.q22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Abdallah</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>ahmed.a9782@gmail.com</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Ulicny</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>johnnyulicny@gmail.com</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Guthrie</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>riley.guthrie1@icloud.com</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Elliott</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>laurenelliottb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Guthrie</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>jack.guthrie@mytools2go.ca</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Michele</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Conlon</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>michele-morgan91@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Martinello</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>svmartinello@outlook.com</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Guthrie</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>r80guthrie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Balliu</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>anjaballiu1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>McQuarrie</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>pmmacquarrie4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Krishnamohan</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>kishanbvg@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Madelyn</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Bondy</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>madelynbon805@gmail.com</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Heth</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Shah</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>heth1998@gmail.com</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Esposito</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>giovanniespo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Vedant</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Khatri</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>khatrivedant10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Litza</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Coello</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>lecahond@gmail.com</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Jas</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Juthani</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>jasjuthani33@gmail.com</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Mihir</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Vora</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>voramihir9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Nitnoy</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Thonglor</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Mohamad</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Mehdi</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>mohamad.h.mehdi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>mihaela</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>birley</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>mihaela.birley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>omar.alpha@gmail.com</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>angus.lam@live.com</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Vong</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Khamwongsa</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Nadine</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Abdallah</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>nadinexo28@gmail.com</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Rakshith</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>rakshith3999@gmail.com</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Alissar</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Mariani</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>alissarhanna@live.ca</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Gandhi</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>gandhineel602@gmail.com</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Rojin</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Golbaz</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>rgolbaz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Eoin</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Minaker</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>eoinminaker66@gmail.com</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Chanhom</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Phalavong</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Windsor.xlsx
+++ b/docs/downloads/Windsor.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15786,6 +15786,606 @@
         </is>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Maciver</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>maciver13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Katia</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Andari</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>mahadevi_ca@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Battaglini</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>maryfrancia@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Delanie</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Cormier-Harris</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Ibrahim</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>feghali</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>ifeghali@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Neve</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Brockbank</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Wayne</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Hall</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>k10hallywood@aol.com</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Katerina</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Lucier</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>katlombardo@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Cormier</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>nataliercormier@gmail.com</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Georgeo</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Ahad</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>kuniva39@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Khosho</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>mike20097.2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>aceman33@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Jaiden</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Berro</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>jayberro23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Irelyn</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Pellitteri</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>kimboih2019@outlook.com</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Galvan</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>ncgalvan21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Mariani</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>pbamariani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Massimo</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Battaglini</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr"/>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Cvitkovic</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>cvitj71@gmail.com</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Haron</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Elashaal</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>haronelashaal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>hudson</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>dalpe</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>dalpehudson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Uttley</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>drewu91@gmail.com</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Battaglini</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>eddiebats23@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Jakowiec</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>alexjakowiec17@gmail.com</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Avery</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Yetman</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>brandoncyetman@gmail.com</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Bri</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Gayle</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>bgayle@newbe.ca</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Harris-Wong</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>erharris6@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Dean</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Flemming</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>dwflemming@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Windsor.xlsx
+++ b/docs/downloads/Windsor.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16386,6 +16386,1368 @@
         </is>
       </c>
     </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Jerry</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>wizkidjdh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Rorai</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>drorai@outlook.com</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Lindsay</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Stradeski</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>lindsaystradeski@gmail.com</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Ellis</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Lucier</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Lian</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>amandalian002@gmail.com</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Branda</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Karana</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>bsyd_14@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Kenneth</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Snart</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>kenneruth@gmail.com</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Venus</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Olla</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>venus_olla@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Gemma</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Wellington</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>brittawellington@gmail.com</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Paige</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Powless</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>ppowless@newbe.ca</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Malaya</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Bayuga</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>malaya.grace88@gmail.com</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Scotty</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Machado</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>scottymachado@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Bayuga</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>fernando.bayuga@gmail.com</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Stacey</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Yannacopoulos</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>s.e.yannacopoulos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Reaume</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>avacreaume@gmail.com</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Melania</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Karana</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Mosure</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>bmosure@newbe.ca</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>castro.p@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>phillygermany91@icloud.com</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Fahad</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Faisail</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>prexforreal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Bashar</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Fatimi</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>basharfatimi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Akinsanya</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>joelakinsanya15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Bassam</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Fatimi</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>bassam.fatimi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Samay</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>samay6ix@gmail.com</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Yorgo</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>yorgohanna2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>eeliajuli@gmail.com</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Reaume</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr"/>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Muhammed</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Aji</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>jymhmd1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Sarra</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>franksarra14@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Noreen</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Reaume</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>noreenreaume@gmail.com</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Sarra</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>ellasarra19@gmail.com</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Firas</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Alkhulaidy</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>falkhulaidy2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Abou-Shanab</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>adamabou216@gmail.com</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Galanopoulos</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>julia2965@icloud.com</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Shayan</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Ghazban</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>shayang36@gmail.com</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Allissa</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Dalla Bona</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>allissadb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Richardson</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>murrayrichardson99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Pranil</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>pranm97@gmail.com</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Hemanth Sai</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Surapuraju</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>hs.iamsoft@gmail.com</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Marissa</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Schenback</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>marissamartin82@gmail.com</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Payne</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>james.g.payne17@gmail.com</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Ola</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Abejide</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>labejide1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Bennett</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>keswickgolfer@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Pare</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>mpare6133@gmail.com</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Deb</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Paling</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>debirish51@gmail.com</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Danlayon</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Mundackal</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>senseb@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Lehoux</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>lehoux.christine@gmail.com</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Rey</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Danlayon</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr"/>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Joanne</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Shepley</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>shepley1412@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Maureen</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Weissenboeck</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>maureenweissenboeck@gmail.com</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Jornith</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Rama</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Musharbash</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>ramamusharbash@gmail.com</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Mady-Gravel</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>suemady@aol.com</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Danlayon</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>donna_mae216@yahoo.com.ph</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Darcie</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Alfini</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>darciealfini@gmail.com</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Jornith</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>jornithbarba@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Dozois</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>maria.dozois@gmail.com</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Moore</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>smoore6244@gmail.com</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Abbey</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Wilkins</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>abbeywilkins2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Trisha</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Pare</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>trishapare1122@gmail.com</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Pare</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>pare.chris25@gmail.com</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Seagris</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>keatingseagris@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>windsor@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
